--- a/data/trans_orig/IP25A01_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17959</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>31702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39625</t>
+          <t>41732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67535</t>
+          <t>68829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87179</t>
+          <t>87760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119886</t>
+          <t>120780</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45757</t>
+          <t>45786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>62592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56326</t>
+          <t>55209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87622</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107185</t>
+          <t>105991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143987</t>
+          <t>143300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33219</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>49124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77511</t>
+          <t>77243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103652</t>
+          <t>102915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>106206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135338</t>
+          <t>135182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190196</t>
+          <t>190833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231035</t>
+          <t>230807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66183</t>
+          <t>66754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91118</t>
+          <t>90902</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,47 +1653,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>35,29%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>48,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>103309</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>88840</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>119137</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>34,99%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>48,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103309</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>89478</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>120772</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>35,24%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>161905</t>
+          <t>162710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>202620</t>
+          <t>202686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24144</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>25281</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>34003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55791</t>
+          <t>56617</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46574</t>
+          <t>46713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94748</t>
+          <t>92994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82246</t>
+          <t>81153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111347</t>
+          <t>109620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137688</t>
+          <t>129400</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195671</t>
+          <t>194801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>55357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122535</t>
+          <t>121549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51337</t>
+          <t>52892</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79583</t>
+          <t>81749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115896</t>
+          <t>116878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189131</t>
+          <t>196439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>26574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22978</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40825</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59938</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>81952</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69152</t>
+          <t>67432</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>90471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133612</t>
+          <t>133850</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>165438</t>
+          <t>164790</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66879</t>
+          <t>67002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88678</t>
+          <t>89988</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66804</t>
+          <t>67896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90714</t>
+          <t>90434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141191</t>
+          <t>140978</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174262</t>
+          <t>173934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31357</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>55948</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>46803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77160</t>
+          <t>76225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114060</t>
+          <t>112334</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158085</t>
+          <t>153959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>243867</t>
+          <t>246619</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>309369</t>
+          <t>311198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>322697</t>
+          <t>325464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>378834</t>
+          <t>381180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588757</t>
+          <t>588608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>677391</t>
+          <t>675183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>259330</t>
+          <t>258461</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>339537</t>
+          <t>338714</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>288335</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>347904</t>
+          <t>345296</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>563647</t>
+          <t>567161</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>664596</t>
+          <t>661852</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A01_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3589</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1165</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9462</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1759</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5119</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10983</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18743</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11084</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6939</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16619</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>52953</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40718</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63528</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>42,06%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32,34%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>50,46%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48805</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>40324</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57202</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>42,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>34,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>49,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56127</t>
+          <t>52082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>42922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68829</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>104932</t>
+          <t>105035</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>89451</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120780</t>
+          <t>118430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58382</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>47042</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72890</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53848</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45786</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62592</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69017</t>
+          <t>54291</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55209</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86643</t>
+          <t>63549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>122864</t>
+          <t>112672</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105991</t>
+          <t>97823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143300</t>
+          <t>130238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>115496</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>115496</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>115496</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>119444</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>119444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>119444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>245350</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>245350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>245350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6926</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14505</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6814</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3194</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>11516</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21232</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14217</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31874</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14405</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8799</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22341</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>34442</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49124</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115086</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>102328</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>129789</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>48,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>89799</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>102915</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>47,48%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>120263</t>
+          <t>86253</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106206</t>
+          <t>74222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135182</t>
+          <t>97162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>210062</t>
+          <t>201339</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190833</t>
+          <t>182488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230807</t>
+          <t>220864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>93014</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>78774</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>106424</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33,34%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>45,05%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>78114</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>66754</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>90902</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>41,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>35,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>48,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>103309</t>
+          <t>77444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88840</t>
+          <t>66259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>88872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>181423</t>
+          <t>170457</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162710</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>202686</t>
+          <t>188172</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>236258</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>236258</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>236258</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>189132</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>189132</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>189132</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>443028</t>
+          <t>419376</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443028</t>
+          <t>419376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>443028</t>
+          <t>419376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1782</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5232</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11646</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5304</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22984</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25281</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19340</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12832</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27540</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>21795</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>12020</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>34003</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>38748</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56617</t>
+          <t>50218</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87188</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>75048</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>100172</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>75461</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>46713</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>92994</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,57%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96530</t>
+          <t>70204</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81153</t>
+          <t>59632</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109620</t>
+          <t>80748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>171991</t>
+          <t>157393</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129400</t>
+          <t>140002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194801</t>
+          <t>174234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>54,31%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77088</t>
+          <t>60031</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55357</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121549</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>65877</t>
+          <t>53586</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81749</t>
+          <t>64918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>142965</t>
+          <t>113617</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116878</t>
+          <t>98750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196439</t>
+          <t>132934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10082</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8681</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8227</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1672</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10112</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16773</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11006</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>24140</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>14,29%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13469</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8374</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19685</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22784</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41043</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74647</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>63619</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>86029</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>37,67%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>50,93%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>70058</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>59198</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>81952</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>42,33%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>49,52%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79748</t>
+          <t>70834</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>60284</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90471</t>
+          <t>82039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>149806</t>
+          <t>145481</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133850</t>
+          <t>130944</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164790</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>73082</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>61766</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>84008</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>43,27%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>49,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>77919</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>67002</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>89988</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>47,08%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>78825</t>
+          <t>76257</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67896</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90434</t>
+          <t>86985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>156744</t>
+          <t>149339</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140978</t>
+          <t>134327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173934</t>
+          <t>163621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>16697</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10396</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>25550</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>24259</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>16804</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>35969</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55948</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>68328</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>55354</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>83056</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>60753</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>46803</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>76225</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>57564</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59199</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>72067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>133798</t>
+          <t>125892</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112334</t>
+          <t>110261</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153959</t>
+          <t>145889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>329874</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>302197</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>353176</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>284123</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>246619</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>311198</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>37,59%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>352667</t>
+          <t>279373</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>325464</t>
+          <t>257937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>381180</t>
+          <t>300503</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>636791</t>
+          <t>609247</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588608</t>
+          <t>578410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>675183</t>
+          <t>642191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>286968</t>
+          <t>284509</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>258461</t>
+          <t>258578</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>338714</t>
+          <t>312152</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>317028</t>
+          <t>261577</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>288335</t>
+          <t>242563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>345296</t>
+          <t>282224</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>603997</t>
+          <t>546085</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>567161</t>
+          <t>514903</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>661852</t>
+          <t>578598</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
